--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard\OneDrive\Kuliah\kuliahSem6\gameprog\gameProgProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95374A5E-2F03-4E96-B0DF-746FE79E16AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86502DFF-1461-49B3-B25A-45581FBB15E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6400" yWindow="1520" windowWidth="19200" windowHeight="10060" xr2:uid="{28291556-F7C6-42AD-907C-0547AB9B3C27}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>hari</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>rey</t>
+  </si>
+  <si>
+    <t>check</t>
+  </si>
+  <si>
+    <t>v</t>
   </si>
 </sst>
 </file>
@@ -440,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C102777E-D56A-4193-9240-67CAB6F4DFB0}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -480,6 +486,20 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richard\OneDrive\Kuliah\kuliahSem6\gameprog\gameProgProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86502DFF-1461-49B3-B25A-45581FBB15E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A06C23-FC78-4545-A9FE-C991798A089A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6400" yWindow="1520" windowWidth="19200" windowHeight="10060" xr2:uid="{28291556-F7C6-42AD-907C-0547AB9B3C27}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>hari</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>v</t>
+  </si>
+  <si>
+    <t>thio</t>
   </si>
 </sst>
 </file>
@@ -485,6 +488,9 @@
       <c r="E2" t="s">
         <v>9</v>
       </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
